--- a/src/test/resources/Team01_RestAssured_Rebels_TestDataSheet.xlsx
+++ b/src/test/resources/Team01_RestAssured_Rebels_TestDataSheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maya/Documents/Maya Numpy Ninja/Team01RestassuredHachathonSep2026/Team01_RestAssured_Rebels/src/test/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dineshdeshmukh/eclipse-workspace/Team01_RestAssured_Rebels/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06EBC8B-FF6E-D84C-A530-E3BB5795B78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0915BA41-9ECC-D14D-8BDD-EBF8FFB07571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-41940" yWindow="1300" windowWidth="35840" windowHeight="18460" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="168">
   <si>
     <t>ScenarioName</t>
   </si>
@@ -266,32 +266,6 @@
   </si>
   <si>
     <t>Create_Valid_User_1</t>
-  </si>
-  <si>
-    <t>{
-  "userFirstName": "Pamm",
-  "userLastName": "Dasd",
-  "userMiddleName": "Pdn",
-  "userPhoneNumber": "&lt;random_phone&gt;",
-  "userLocation": "Atlanta",
-  "userTimeZone": "EST",
-  "userLinkedinUrl": "www.linkedin.com",
-  "userEduUg": "BE",
-  "userEduPg": "PHD",
-  "userComments": "PASSED",
-  "userVisaStatus": "H1B",
-  "userRoleMaps": [
-    {
-      "roleId": "R02",
-      "userRoleStatus": "Active"
-    }
-  ],
-  "userLogin": {
-    "userLoginEmail": "&lt;random_email&gt;",
-    "loginStatus": "Active",
-    "status": "Active"
-  }
-}</t>
   </si>
   <si>
     <t xml:space="preserve"> /users/roleStatus</t>
@@ -329,9 +303,6 @@
 }</t>
   </si>
   <si>
-    <t>Create_User_Only_Mandatory_Fields</t>
-  </si>
-  <si>
     <t>{
   "userFirstName": "Pamm",
   "userLastName": "Dasd",
@@ -356,94 +327,39 @@
     <t>/users/roleStatus</t>
   </si>
   <si>
-    <t>Get_All_Users_Valid</t>
-  </si>
-  <si>
-    <t>/users</t>
-  </si>
-  <si>
-    <t>Get_All_Users_Invalid_Endpoint</t>
-  </si>
-  <si>
-    <t>users/invalid</t>
-  </si>
-  <si>
-    <t>Get_All_Users_Invalid_Method</t>
-  </si>
-  <si>
-    <t>GetAllUsers_Without_Authorization</t>
-  </si>
-  <si>
-    <t>Get_Active_Inactive_User_Count_All</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[
-  {
-    "status": "Active",
-    "count": 369
+    <t>Auth</t>
+  </si>
+  <si>
+    <t>ContentType</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Neha",
+  "userLastName": "Patel",
+  "userMiddleName": "Das",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "PHD",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R02",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
   }
-]
-</t>
-  </si>
-  <si>
-    <t>users/byStatus</t>
-  </si>
-  <si>
-    <t>GET</t>
-  </si>
-  <si>
-    <t>Get_Active_Inactive_User_Count_R01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-  {
-    "status": "Active",
-    "count": 21
-  }
-]</t>
-  </si>
-  <si>
-    <t>Get_Active_Inactive_User_Count_R02</t>
-  </si>
-  <si>
-    <t>[
-  {
-    "status": "Active",
-    "count": 195
-  }
-]</t>
-  </si>
-  <si>
-    <t>Get_Active_Inactive_User_Count_R03</t>
-  </si>
-  <si>
-    <t>[
-  {
-    "status": "Active",
-    "count": 157
-  }
-]</t>
-  </si>
-  <si>
-    <t>Get_Active_Inactive_User_Count_Invalid_RoleID</t>
-  </si>
-  <si>
-    <t>{
-  "message": "RoleID R04 not found",
-  "success": false
 }</t>
   </si>
   <si>
-    <t>Get_Active_Inactive_User_Count_Invalid_Endpoint</t>
-  </si>
-  <si>
-    <t>users/byStatu</t>
-  </si>
-  <si>
-    <t>Get_Active_Inactive_User_Count_Invalid_Method</t>
-  </si>
-  <si>
-    <t>Get_Active_Inactive_User_Count_Without_Authorization</t>
+    <t>application/json</t>
   </si>
   <si>
     <t>{
@@ -451,7 +367,7 @@
   "userLastName": "penny",
   "userMiddleName": "jonn",
   "userPhoneNumber": "&lt;random_phone&gt;",
-  "userLocation": "Atlanta",
+    "userLocation": "Atlanta",
   "userTimeZone": "EST",
   "userLinkedinUrl": "www.linkedin.com",
   "userEduUg": "BE",
@@ -472,176 +388,862 @@
 }</t>
   </si>
   <si>
-    <t>CreateBatch_Invalid_endpoint</t>
+    <t>Create_User_Only_Mandatory_Field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create_User_Empty_Payload </t>
   </si>
   <si>
     <t>{
-"batchDescription": "Test",
-"batchName": "Batch1",
-"batchNoOfClasses": 1,
-"batchStatus": "Active",
-"programId": 66
 }</t>
   </si>
   <si>
-    <t>/batch</t>
-  </si>
-  <si>
-    <t>CreateBatch_Invalid_BatchDescription</t>
+    <t>Create_User_Empty_Frist_Name_Field</t>
+  </si>
+  <si>
+    <t>Create_User_Empty_Last_Name_Field</t>
   </si>
   <si>
     <t>{
-"batchDescription": "@@",
-"batchName": "pithongjagijjjngZO_865",
-"batchNoOfClasses": 1,
-"batchStatus": "Active",
-"programId": 66
+  "userFirstName": "Sunny",
+  "userLastName": " ",
+  "userMiddleName": "Desi",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "PHD",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R02",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
 }</t>
   </si>
   <si>
-    <t>must begin with letter</t>
+    <t>Create_User_Empty_Location</t>
   </si>
   <si>
     <t>{
-    "batchDescription": "Batch Description must be of min length 4 and max length 25."
+  "userFirstName": "Sunny",
+  "userLastName": "Patil",
+  "userMiddleName": "Desi",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "PHD",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R02",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
 }</t>
   </si>
   <si>
+    <t>Create_User_Empty_TimeZone</t>
+  </si>
+  <si>
     <t>{
-    "batchDescription": "batchDescription must begin with letter and can only have letters, numbers, comma, hyphen, colon, period, underscore and space"
+  "userFirstName": "Sunny",
+  "userLastName": "Penny","userMiddleName": "Desi",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R01",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
 }</t>
   </si>
   <si>
-    <t>CreateBatch_Invalid_BatchName</t>
+    <t>Create_User_Empty_VisaStatus</t>
   </si>
   <si>
     <t>{
-"batchDescription": "ab",
-"batchName": "123456",
-"batchNoOfClasses": 1,
-"batchStatus": "Active",
-"programId": 66
+  "userFirstName": "Sunny",
+  "userLastName": "Penny",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userVisaStatus": "",
+  "userRoleMaps": [
+    {
+      "roleId": "R01",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
 }</t>
   </si>
   <si>
-    <t>Batch Description must be of min</t>
+    <t xml:space="preserve">Create_User_Empty_RoleId </t>
   </si>
   <si>
     <t>{
-    "batchName": "batchName Must be in the format of ProgramName_&lt;number&gt;",
-    "batchDescription": "Batch Description must be of min length 4 and max length 25."
+  "userFirstName": "Sunny",
+  "userLastName": "Penny",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userVisaStatus": "H4",
+  "userRoleMaps": [
+    {
+      "roleId": "",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
 }</t>
   </si>
   <si>
-    <t>CreateBatch_Invalid_BatchNoOfClasses</t>
+    <t>Create_User_Empty_RoleStatus</t>
   </si>
   <si>
     <t>{
-"batchDescription": "ab",
-"batchName": "pithongjagijjjngZO_865",
-"batchNoOfClasses": "ten",
-"batchStatus": "Active",
-"programId": 66
+  "userFirstName": "Sunny",
+  "userLastName": "Penny",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userVisaStatus": "H4",
+  "userRoleMaps": [
+    {
+      "roleId": "R03",
+      "userRoleStatus": ""
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
 }</t>
   </si>
   <si>
-    <t>batchNoOfClasses must be a whole integer</t>
-  </si>
-  <si>
-    <t>CreateBatch_Invalid_BatchNameLength</t>
+    <t>Create_User_Empty_LoginStatus</t>
   </si>
   <si>
     <t>{
-"batchDescription": "ab",
-"batchName": "Test",
-"batchNoOfClasses": 1,
-"batchStatus": "Active",
-"programId": 66
+  "userFirstName": "Sunny",
+  "userLastName": "Penny",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userVisaStatus": "H4",
+  "userRoleMaps": [
+    {
+      "roleId": "R03",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": " ",
+    "status": "Active"
+  }
 }</t>
   </si>
   <si>
-    <t>Batch Description must be of min length 4 and max length 25</t>
-  </si>
-  <si>
-    <t>CreateBatch_Invalid_BatchStatus</t>
+    <t xml:space="preserve">Create_User_Empty_Email </t>
   </si>
   <si>
     <t>{
-"batchDescription": "TestPlaywright",
-"batchName": "pithongjagijjjngZO_865",
-"batchNoOfClasses": 1,
-"batchStatus": "wrong",
-"programId": 66
+  "userFirstName": "Sunny",
+  "userLastName": "Penny",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userVisaStatus": "H4",
+  "userRoleMaps": [
+    {
+      "roleId": "R03",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
 }</t>
   </si>
   <si>
-    <t>Invalid Status: must be Active or Inactive</t>
-  </si>
-  <si>
-    <t>CreateBatch_Invalid_ProgramId</t>
+    <t>Create_User_Empty_PhoneNumber</t>
   </si>
   <si>
     <t>{
-"batchDescription": "TestPlaywright",
-"batchName": "pithongjagijjjngZO_865",
-"batchNoOfClasses": 1,
-"batchStatus": "Active",
-"programId": 00000a0
+  "userFirstName": "Sunny",
+  "userLastName": "Penny",
+  "userPhoneNumber": "",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R01",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
 }</t>
   </si>
   <si>
-    <t>JSON parse error: Invalid numeric value</t>
-  </si>
-  <si>
-    <t>CreateBatch_Inactive_ProgramId</t>
+    <t>Create_User_Duplicate_Email</t>
   </si>
   <si>
     <t>{
-"batchDescription": "Test",
-"batchName": "pithongjagijjjngZO_865",
-"batchNoOfClasses": 1,
-"batchStatus": "Active",
-"programId": 1
+  "userFirstName": "Sunny",
+  "userLastName": "Penny","userMiddleName": "Desi",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R01",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "Team01@gmail.com",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
 }</t>
   </si>
   <si>
-    <t>Batch cannot be created for a Program with Inactive status</t>
-  </si>
-  <si>
-    <t>GetAll_Valid_Batches</t>
-  </si>
-  <si>
-    <t>GetAll_Batches_InvalidEndpoint</t>
-  </si>
-  <si>
-    <t>GetAll_Batches_With_NoAuth</t>
-  </si>
-  <si>
-    <t>GetAll_BatchById_Valid_BatchId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/batches/batchId/{batchId}
+    <t>Create_User_Duplicate_Phone_Number</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Sunny",
+  "userLastName": "Penny",
+  "userPhoneNumber": "+91 9158758687",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R01",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_UserEduPg</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Sunny",
+  "userLastName": "Patil",
+  "userMiddleName": "Desi",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "123",
+  "userEduPg": "PHD",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R02",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_UserEduUg</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Sunny",
+  "userLastName": "Patil",
+  "userMiddleName": "Desi",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "12356",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R02",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_First_Name</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "123",
+  "userLastName": "Patil",
+  "userMiddleName": "Desi",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "phd",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R02",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_Last_Name</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Saloni",
+  "userLastName": "123",
+  "userMiddleName": "Desi",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "phd",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R02",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_Middle_Name</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Saloni",
+  "userLastName": "Dubey",
+  "userMiddleName": "123",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "Phd",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R02",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_UserLinkedinUrl</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Saloni",
+  "userLastName": "Dubey",
+  "userMiddleName": "das",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedinnnnn.in",
+  "userEduUg": "BE",
+  "userEduPg": "PHD",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R02",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_UserLocation</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Saloni",
+  "userLastName": "Dubey",
+  "userMiddleName": "das",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "123",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "PHD",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R02",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_Phone_Number_Format</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Saloni",
+  "userLastName": "Dubey",
+  "userMiddleName": "das",
+  "userPhoneNumber": " 5647839212. +91",
+  "userLocation": "India",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "PHD",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R02",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_User_Role_Id</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Saloni",
+  "userLastName": "Dubey",
+  "userMiddleName": "das",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "123",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "PHD",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R2",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_User_Role_Status</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Saloni",
+  "userLastName": "Dubey",
+  "userMiddleName": "das",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "India",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "PHD",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R03",
+      "userRoleStatus": "Present"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_User_Time_Zone</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Saloni",
+  "userLastName": "Dubey",
+  "userMiddleName": "das",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "India",
+  "userTimeZone": "PT",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "PHD",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R03",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_User_Visa_Status</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Saloni",
+  "userLastName": "Dubey",
+  "userMiddleName": "das",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "India",
+  "userTimeZone": "IST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "PHD",
+  "userComments": "PASSED",
+  "userVisaStatus": "NONE",
+  "userRoleMaps": [
+    {
+      "roleId": "R03",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_Token</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": "Saloni",
+  "userLastName": "Dubey",
+  "userMiddleName": "das",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "India",
+  "userTimeZone": "IST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "PHD",
+  "userComments": "PASSED",
+  "userVisaStatus": "NA",
+  "userRoleMaps": [
+    {
+      "roleId": "R03",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_Endpoint</t>
+  </si>
+  <si>
+    <t>/api/v1/invalidpath123</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_Content_Type</t>
+  </si>
+  <si>
+    <t>text/plain</t>
+  </si>
+  <si>
+    <t>Create_User_Invalid_Method</t>
+  </si>
+  <si>
+    <t>Create_User_No_Auth</t>
+  </si>
+  <si>
+    <t>Get_All_Active_Users_Success</t>
+  </si>
+  <si>
+    <t>/users/activeUsers</t>
+  </si>
+  <si>
+    <t>GET</t>
+  </si>
+  <si>
+    <t>Get_All_Active_Users_Invalid_Endpoint</t>
+  </si>
+  <si>
+    <t>/use/activeUsers</t>
+  </si>
+  <si>
+    <t>Get_All_Active_Users_Invalid_Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Get_All_Active_Users_No_Auth </t>
+  </si>
+  <si>
+    <t>Get_Active_User_Emails_Valid_Endpoint</t>
+  </si>
+  <si>
+    <t>/fetch-emails</t>
+  </si>
+  <si>
+    <t>Get_Active_User_Emails_Invalid_Endpoint</t>
+  </si>
+  <si>
+    <t>/fetch-Invalidemailseeeee</t>
+  </si>
+  <si>
+    <t>Get_Active_User_Emails_Invalid_Method</t>
+  </si>
+  <si>
+    <t>Get_Active_User_Emails_No_Auth</t>
+  </si>
+  <si>
+    <t>Get_All_Roles_Valid_Endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> /users/roles</t>
+  </si>
+  <si>
+    <t>Get_All_Roles_Invalid_Endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> invalid/users/roles</t>
+  </si>
+  <si>
+    <t>Get_All_Roles_Invalid_Method</t>
+  </si>
+  <si>
+    <t>Get_All_Roles_No_Auth</t>
+  </si>
+  <si>
+    <t>Get_All_Users_Valid</t>
+  </si>
+  <si>
+    <t>/users</t>
+  </si>
+  <si>
+    <t>Get_All_Users_Invalid_Endpoint</t>
+  </si>
+  <si>
+    <t>users/invalid</t>
+  </si>
+  <si>
+    <t>Get_All_Users_Invalid_Method</t>
+  </si>
+  <si>
+    <t>GetAllUsers_Without_Authorization</t>
+  </si>
+  <si>
+    <t>Get_Active_Inactive_User_Count_All</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[
+  {
+    "status": "Active",
+    "count": 369
+  }
+]
 </t>
   </si>
   <si>
-    <t>GetBatchById_InvalidBatchId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/batches/batchId/9999
-</t>
-  </si>
-  <si>
-    <t>Batch not found with Id</t>
-  </si>
-  <si>
-    <t>GetBatch_ById_NoAuth</t>
-  </si>
-  <si>
-    <t>GetBatchById_Invalid_Endpoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/batches/batid/9999
-</t>
+    <t>users/byStatus</t>
+  </si>
+  <si>
+    <t>Get_Active_Inactive_User_Count_R01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+  {
+    "status": "Active",
+    "count": 21
+  }
+]</t>
+  </si>
+  <si>
+    <t>Get_Active_Inactive_User_Count_R02</t>
+  </si>
+  <si>
+    <t>[
+  {
+    "status": "Active",
+    "count": 195
+  }
+]</t>
+  </si>
+  <si>
+    <t>Get_Active_Inactive_User_Count_R03</t>
+  </si>
+  <si>
+    <t>[
+  {
+    "status": "Active",
+    "count": 157
+  }
+]</t>
+  </si>
+  <si>
+    <t>Get_Active_Inactive_User_Count_Invalid_RoleID</t>
+  </si>
+  <si>
+    <t>{
+  "message": "RoleID R04 not found",
+  "success": false
+}</t>
+  </si>
+  <si>
+    <t>Get_Active_Inactive_User_Count_Invalid_Endpoint</t>
+  </si>
+  <si>
+    <t>users/byStatu</t>
+  </si>
+  <si>
+    <t>Get_Active_Inactive_User_Count_Invalid_Method</t>
+  </si>
+  <si>
+    <t>Get_Active_Inactive_User_Count_Without_Authorization</t>
+  </si>
+  <si>
+    <t>DELETE</t>
+  </si>
+  <si>
+    <t>{
+  "userFirstName": ""  ,
+  "userLastName": "Mathur",
+  "userMiddleName": "Desi",
+  "userPhoneNumber": "&lt;random_phone&gt;",
+  "userLocation": "Atlanta",
+  "userTimeZone": "EST",
+  "userLinkedinUrl": "www.linkedin.com",
+  "userEduUg": "BE",
+  "userEduPg": "PHD",
+  "userComments": "PASSED",
+  "userVisaStatus": "H1B",
+  "userRoleMaps": [
+    {
+      "roleId": "R02",
+      "userRoleStatus": "Active"
+    }
+  ],
+  "userLogin": {
+    "userLoginEmail": "&lt;random_email&gt;",
+    "loginStatus": "Active",
+    "status": "Active"
+  }
+}</t>
   </si>
 </sst>
 </file>
@@ -671,6 +1273,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
@@ -693,27 +1301,20 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -724,12 +1325,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -745,7 +1340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -753,53 +1348,53 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1024,7 +1619,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:7" ht="47" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1038,7 +1633,7 @@
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2"/>
@@ -1051,7 +1646,7 @@
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2"/>
@@ -1064,12 +1659,12 @@
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="5"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>415</v>
       </c>
       <c r="E5" s="2"/>
@@ -1077,12 +1672,12 @@
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>401</v>
       </c>
       <c r="E6" s="2"/>
@@ -1090,10 +1685,10 @@
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" ht="56" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="2"/>
@@ -1105,10 +1700,10 @@
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" ht="64" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="2"/>
@@ -1120,10 +1715,10 @@
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" ht="70" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="2"/>
@@ -1138,7 +1733,7 @@
       <c r="A10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="2"/>
@@ -1150,10 +1745,10 @@
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" ht="56" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="2"/>
@@ -1165,10 +1760,10 @@
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" ht="56" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="2"/>
@@ -1180,10 +1775,10 @@
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" ht="56" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="2"/>
@@ -1195,10 +1790,10 @@
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" ht="56" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="2"/>
@@ -1210,10 +1805,10 @@
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" ht="56" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="2"/>
@@ -1225,10 +1820,10 @@
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" ht="56" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C16" s="2"/>
@@ -1240,7 +1835,7 @@
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="2"/>
@@ -1254,7 +1849,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
-      <c r="B18" s="6"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -1344,7 +1939,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
-      <c r="B28" s="5"/>
+      <c r="B28" s="3"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -1362,7 +1957,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
-      <c r="B30" s="5"/>
+      <c r="B30" s="3"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -1390,7 +1985,7 @@
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="8"/>
+      <c r="C33" s="9"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -10137,12 +10732,12 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B11" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B12" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B14" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B15" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B16" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="B11" r:id="rId1" display="pasha.12@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B12" r:id="rId2" display="Team01@gmail.com" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B13" r:id="rId3" display="Team01@gmail.com" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B14" r:id="rId4" display="Team01@gmail.com" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="B15" r:id="rId5" display="Team01@gmail.com" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B16" r:id="rId6" display="inactive@gmail.com" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -10151,7 +10746,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.33203125" customWidth="1"/>
@@ -10177,20 +10772,20 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" spans="1:13" ht="105" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>32</v>
       </c>
       <c r="C2" t="s">
@@ -10199,328 +10794,103 @@
       <c r="D2">
         <v>201</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
     </row>
     <row r="3" spans="1:13" ht="105" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="14">
         <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="105" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="14">
         <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="105" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="14">
         <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="105" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="14">
         <v>400</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="15" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="105" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="14">
         <v>401</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="105" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="14">
         <v>400</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="12" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="99" x14ac:dyDescent="0.2">
-      <c r="A9" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" s="19">
-        <v>404</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="350" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="19">
-        <v>400</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="365" x14ac:dyDescent="0.2">
-      <c r="A11" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="19">
-        <v>400</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="99" x14ac:dyDescent="0.2">
-      <c r="A12" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="19">
-        <v>400</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="99" x14ac:dyDescent="0.2">
-      <c r="A13" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="19">
-        <v>400</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="99" x14ac:dyDescent="0.2">
-      <c r="A14" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="19">
-        <v>400</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="99" x14ac:dyDescent="0.2">
-      <c r="A15" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="19">
-        <v>400</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="99" x14ac:dyDescent="0.2">
-      <c r="A16" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="19">
-        <v>400</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="19">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18" s="19">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="19">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20" s="19">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A21" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" s="19">
-        <v>404</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22" s="19">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A23" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="D23" s="19">
-        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -10534,119 +10904,118 @@
   <dimension ref="A1:Z3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.6640625" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" customWidth="1"/>
     <col min="5" max="5" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="10"/>
+      <c r="Z1" s="10"/>
     </row>
     <row r="2" spans="1:26" ht="183" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="10">
         <v>201</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+      <c r="Z2" s="10"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10656,256 +11025,1033 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32" style="3" customWidth="1"/>
-    <col min="2" max="2" width="61.1640625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="3"/>
+    <col min="1" max="1" width="60.5" style="4" customWidth="1"/>
+    <col min="2" max="2" width="65" style="4" customWidth="1"/>
+    <col min="3" max="16384" width="8.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="333" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
+      <c r="E1" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="332" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="D2" s="17">
+        <v>201</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="15">
+      <c r="B3" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="18">
         <v>201</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="395" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
+      <c r="E3" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A4" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="18">
+        <v>201</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+      <c r="A5" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="18">
+        <v>201</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+      <c r="A6" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="18">
+        <v>400</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+    </row>
+    <row r="7" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="18">
+        <v>400</v>
+      </c>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+    </row>
+    <row r="8" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A8" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="18">
+        <v>400</v>
+      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+    </row>
+    <row r="9" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A9" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="18">
+        <v>400</v>
+      </c>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+    </row>
+    <row r="10" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+      <c r="A10" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="18">
+        <v>400</v>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+      <c r="A11" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="18">
+        <v>400</v>
+      </c>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+      <c r="A12" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="18">
+        <v>400</v>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+      <c r="A13" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="18">
+        <v>400</v>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+      <c r="A14" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="18">
+        <v>400</v>
+      </c>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+      <c r="A15" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="3">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="380" x14ac:dyDescent="0.2">
-      <c r="A4" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="3">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="304" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+      <c r="C15" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D15" s="18">
+        <v>400</v>
+      </c>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+      <c r="A16" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="18">
+        <v>400</v>
+      </c>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+    </row>
+    <row r="17" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+      <c r="A17" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="18">
+        <v>400</v>
+      </c>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+      <c r="A18" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="18">
+        <v>400</v>
+      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+    </row>
+    <row r="19" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A19" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="18">
+        <v>400</v>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+    </row>
+    <row r="20" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A20" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="18">
+        <v>400</v>
+      </c>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+    </row>
+    <row r="21" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A21" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="18">
+        <v>400</v>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="22" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A22" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="18">
+        <v>400</v>
+      </c>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+    </row>
+    <row r="23" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A23" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="18">
+        <v>400</v>
+      </c>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+    </row>
+    <row r="24" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A24" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="18">
+        <v>400</v>
+      </c>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+    </row>
+    <row r="25" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A25" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="18">
+        <v>400</v>
+      </c>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+    </row>
+    <row r="26" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A26" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="18">
+        <v>400</v>
+      </c>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+    </row>
+    <row r="27" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A27" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="18">
+        <v>400</v>
+      </c>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+    </row>
+    <row r="28" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A28" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="18">
+        <v>400</v>
+      </c>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+    </row>
+    <row r="29" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A29" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="18">
+        <v>400</v>
+      </c>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+    </row>
+    <row r="30" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A30" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" s="18">
+        <v>400</v>
+      </c>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+    </row>
+    <row r="31" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A31" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="18">
+        <v>401</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31" s="18"/>
+    </row>
+    <row r="32" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A32" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="18">
+        <v>404</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="3">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6"/>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6">
+      <c r="F32" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="33" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A33" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="18">
+        <v>415</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" s="18"/>
+      <c r="G33" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A34" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34" s="18">
+        <v>405</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="G34" s="18"/>
+    </row>
+    <row r="35" spans="1:7" ht="380" x14ac:dyDescent="0.2">
+      <c r="A35" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="18">
+        <v>401</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G35" s="18"/>
+    </row>
+    <row r="36" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A36" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" s="18">
         <v>200</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7"/>
-      <c r="C7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7">
+      <c r="E36" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G36" s="18"/>
+    </row>
+    <row r="37" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A37" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" s="18">
         <v>404</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8"/>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8">
+      <c r="E37" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G37" s="18"/>
+    </row>
+    <row r="38" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A38" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="18">
         <v>405</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9"/>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9">
+      <c r="E38" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G38" s="18"/>
+    </row>
+    <row r="39" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A39" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D39" s="18">
         <v>401</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10">
+      <c r="E39" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G39" s="18"/>
+    </row>
+    <row r="40" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A40" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D40" s="18">
         <v>200</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="96" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11">
+      <c r="E40" s="18"/>
+      <c r="F40" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G40" s="18"/>
+    </row>
+    <row r="41" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A41" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D41" s="18">
+        <v>404</v>
+      </c>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G41" s="18"/>
+    </row>
+    <row r="42" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A42" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D42" s="18">
+        <v>405</v>
+      </c>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G42" s="18"/>
+    </row>
+    <row r="43" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="A43" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="D43" s="18">
+        <v>401</v>
+      </c>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G43" s="18"/>
+    </row>
+    <row r="44" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A44" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D44" s="18">
         <v>200</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="96" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12">
+      <c r="E44" s="18"/>
+      <c r="F44" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G44" s="18"/>
+    </row>
+    <row r="45" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A45" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D45" s="18">
+        <v>404</v>
+      </c>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G45" s="18"/>
+    </row>
+    <row r="46" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A46" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D46" s="18">
+        <v>405</v>
+      </c>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G46" s="18"/>
+    </row>
+    <row r="47" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="A47" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D47" s="18">
+        <v>401</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="F47" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="G47" s="18"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>145</v>
+      </c>
+      <c r="B48"/>
+      <c r="C48" t="s">
+        <v>146</v>
+      </c>
+      <c r="D48">
         <v>200</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="96" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>147</v>
+      </c>
+      <c r="B49"/>
+      <c r="C49" t="s">
+        <v>148</v>
+      </c>
+      <c r="D49">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>149</v>
+      </c>
+      <c r="B50"/>
+      <c r="C50" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>150</v>
+      </c>
+      <c r="B51"/>
+      <c r="C51" t="s">
+        <v>146</v>
+      </c>
+      <c r="D51">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="112" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>151</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" t="s">
+        <v>153</v>
+      </c>
+      <c r="D52">
         <v>200</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="E52" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C53" t="s">
+        <v>153</v>
+      </c>
+      <c r="D53">
+        <v>200</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C54" t="s">
+        <v>153</v>
+      </c>
+      <c r="D54">
+        <v>200</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="96" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C55" t="s">
+        <v>153</v>
+      </c>
+      <c r="D55">
+        <v>200</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C56" t="s">
+        <v>153</v>
+      </c>
+      <c r="D56" s="4">
         <v>404</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" s="3">
+      <c r="E56" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D57" s="4">
         <v>404</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="3">
+    <row r="58" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C58" t="s">
+        <v>153</v>
+      </c>
+      <c r="D58" s="4">
         <v>405</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E58" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="3">
+    <row r="59" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C59" t="s">
+        <v>153</v>
+      </c>
+      <c r="D59" s="4">
         <v>401</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>73</v>
+      <c r="E59" s="4" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/Team01_RestAssured_Rebels_TestDataSheet.xlsx
+++ b/src/test/resources/Team01_RestAssured_Rebels_TestDataSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maya/Documents/Maya Numpy Ninja/Team01RestassuredHachathonSep2026/pramodini/Team01_RestAssured_Rebels/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC21B0C-8BE8-A946-848D-99257A989D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E1C6AC-3690-2F42-B1DC-FC9AD1D5A5D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17060" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -82,13 +82,6 @@
     <t>Create_NewProgram</t>
   </si>
   <si>
-    <t>{
-"programDescription": "pithon",
-"programName": "pithongjagijjjng",
-"programStatus": "Active"
-}</t>
-  </si>
-  <si>
     <t>/saveprogram</t>
   </si>
   <si>
@@ -937,6 +930,13 @@
   </si>
   <si>
     <t>Get_All_Users_Valid</t>
+  </si>
+  <si>
+    <t>{
+"programDescription": "pithon",
+"programName": "pithjjgjagijjjng",
+"programStatus": "Active"
+}</t>
   </si>
 </sst>
 </file>
@@ -1088,9 +1088,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1476,7 +1476,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1489,7 +1489,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1501,11 +1501,11 @@
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>62</v>
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="22">
@@ -1516,9 +1516,9 @@
       <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A8" s="21"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
@@ -1527,9 +1527,9 @@
       <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A9" s="21"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" s="22"/>
       <c r="D9" s="22"/>
@@ -1538,9 +1538,9 @@
       <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A10" s="21"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
@@ -1549,11 +1549,11 @@
       <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="21" t="s">
-        <v>66</v>
+      <c r="A11" s="23" t="s">
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" s="22"/>
       <c r="D11" s="22">
@@ -1564,9 +1564,9 @@
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="21"/>
+      <c r="A12" s="23"/>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
@@ -1575,9 +1575,9 @@
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="21"/>
+      <c r="A13" s="23"/>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
@@ -1586,9 +1586,9 @@
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="21"/>
+      <c r="A14" s="23"/>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" s="22"/>
       <c r="D14" s="22"/>
@@ -1597,11 +1597,11 @@
       <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="21" t="s">
-        <v>69</v>
+      <c r="A15" s="23" t="s">
+        <v>68</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" s="22">
         <v>400</v>
@@ -1612,9 +1612,9 @@
       <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="21"/>
+      <c r="A16" s="23"/>
       <c r="B16" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16" s="22"/>
       <c r="D16" s="22"/>
@@ -1623,9 +1623,9 @@
       <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="21"/>
+      <c r="A17" s="23"/>
       <c r="B17" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
@@ -1634,9 +1634,9 @@
       <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="22"/>
@@ -1645,11 +1645,11 @@
       <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="23" t="s">
-        <v>72</v>
+      <c r="A19" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" s="22">
         <v>400</v>
@@ -1660,9 +1660,9 @@
       <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="23"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="22"/>
@@ -1671,9 +1671,9 @@
       <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="23"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" s="22"/>
       <c r="D21" s="22"/>
@@ -1682,9 +1682,9 @@
       <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="23"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22" s="22"/>
       <c r="D22" s="22"/>
@@ -1693,107 +1693,107 @@
       <c r="G22" s="5"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="21" t="s">
-        <v>75</v>
+      <c r="A23" s="23" t="s">
+        <v>74</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="21">
+        <v>61</v>
+      </c>
+      <c r="C23" s="23">
         <v>400</v>
       </c>
-      <c r="D23" s="21"/>
+      <c r="D23" s="23"/>
       <c r="E23"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="21"/>
+      <c r="A24" s="23"/>
       <c r="B24" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
+        <v>75</v>
+      </c>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
       <c r="E24"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="21"/>
+      <c r="A25" s="23"/>
       <c r="B25" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
+        <v>63</v>
+      </c>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
       <c r="E25"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="21"/>
+      <c r="A26" s="23"/>
       <c r="B26" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
+        <v>64</v>
+      </c>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
       <c r="E26"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="21" t="s">
-        <v>77</v>
+      <c r="A27" s="23" t="s">
+        <v>76</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="21">
+        <v>61</v>
+      </c>
+      <c r="C27" s="23">
         <v>400</v>
       </c>
-      <c r="D27" s="21"/>
+      <c r="D27" s="23"/>
       <c r="E27"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="21"/>
+      <c r="A28" s="23"/>
       <c r="B28" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
+        <v>77</v>
+      </c>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
       <c r="E28"/>
       <c r="F28" s="5"/>
       <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="21"/>
+      <c r="A29" s="23"/>
       <c r="B29" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
+        <v>78</v>
+      </c>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
       <c r="E29"/>
       <c r="F29" s="5"/>
       <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="21"/>
+      <c r="A30" s="23"/>
       <c r="B30" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
+        <v>64</v>
+      </c>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
       <c r="E30"/>
       <c r="F30" s="5"/>
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="23" t="s">
-        <v>80</v>
+      <c r="A31" s="21" t="s">
+        <v>79</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31" s="22">
         <v>400</v>
@@ -1804,9 +1804,9 @@
       <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="23"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="22"/>
@@ -1815,9 +1815,9 @@
       <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="22"/>
@@ -1826,9 +1826,9 @@
       <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="23"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C34" s="22"/>
       <c r="D34" s="22"/>
@@ -1837,59 +1837,59 @@
       <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="23" t="s">
-        <v>82</v>
+      <c r="A35" s="21" t="s">
+        <v>81</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" s="23">
+        <v>61</v>
+      </c>
+      <c r="C35" s="21">
         <v>400</v>
       </c>
-      <c r="D35" s="23"/>
+      <c r="D35" s="21"/>
       <c r="E35"/>
       <c r="F35" s="5"/>
       <c r="G35" s="7"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="23"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
+        <v>77</v>
+      </c>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
       <c r="E36"/>
       <c r="F36" s="5"/>
       <c r="G36" s="7"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="23"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
+        <v>82</v>
+      </c>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
       <c r="E37"/>
       <c r="F37" s="5"/>
       <c r="G37" s="7"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="23"/>
+      <c r="A38" s="21"/>
       <c r="B38" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
+        <v>64</v>
+      </c>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
       <c r="E38"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="23" t="s">
-        <v>84</v>
+      <c r="A39" s="21" t="s">
+        <v>83</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C39" s="22">
         <v>400</v>
@@ -1900,9 +1900,9 @@
       <c r="G39" s="7"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="23"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C40" s="22"/>
       <c r="D40" s="22"/>
@@ -1911,9 +1911,9 @@
       <c r="G40" s="7"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="23"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C41" s="22"/>
       <c r="D41" s="22"/>
@@ -1922,9 +1922,9 @@
       <c r="G41" s="7"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="23"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C42" s="22"/>
       <c r="D42" s="22"/>
@@ -1933,11 +1933,11 @@
       <c r="G42" s="7"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="23" t="s">
-        <v>86</v>
+      <c r="A43" s="21" t="s">
+        <v>85</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43" s="22">
         <v>400</v>
@@ -1948,9 +1948,9 @@
       <c r="G43" s="7"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="23"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C44" s="22"/>
       <c r="D44" s="22"/>
@@ -1959,9 +1959,9 @@
       <c r="G44" s="7"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="23"/>
+      <c r="A45" s="21"/>
       <c r="B45" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C45" s="22"/>
       <c r="D45" s="22"/>
@@ -1970,9 +1970,9 @@
       <c r="G45" s="7"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="23"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C46" s="22"/>
       <c r="D46" s="22"/>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -10608,30 +10608,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="D39:D42"/>
-    <mergeCell ref="A43:A46"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="D31:D34"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="C35:C38"/>
-    <mergeCell ref="D35:D38"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="D27:D30"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="D15:D18"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="C19:C22"/>
-    <mergeCell ref="D19:D22"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="D7:D10"/>
@@ -10640,6 +10616,30 @@
     <mergeCell ref="C11:C14"/>
     <mergeCell ref="D11:D14"/>
     <mergeCell ref="E11:E14"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="C19:C22"/>
+    <mergeCell ref="D19:D22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="D27:D30"/>
+    <mergeCell ref="A31:A34"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="D31:D34"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="C35:C38"/>
+    <mergeCell ref="D35:D38"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="D39:D42"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="C43:C46"/>
+    <mergeCell ref="D43:D46"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B23" r:id="rId1" display="mailto:pasha.12@gmail.com" xr:uid="{BC0A013B-9365-F349-822B-39DC9F6A3FCC}"/>
@@ -10693,7 +10693,7 @@
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="3"/>
@@ -10727,10 +10727,10 @@
     </row>
     <row r="3" spans="1:13" ht="270" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>91</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>92</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>8</v>
@@ -10741,10 +10741,10 @@
     </row>
     <row r="4" spans="1:13" ht="255" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>93</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>94</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>8</v>
@@ -10755,10 +10755,10 @@
     </row>
     <row r="5" spans="1:13" ht="285" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>95</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>96</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>8</v>
@@ -10769,10 +10769,10 @@
     </row>
     <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>97</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>98</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>8</v>
@@ -10781,15 +10781,15 @@
         <v>400</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>8</v>
@@ -10800,10 +10800,10 @@
     </row>
     <row r="8" spans="1:13" ht="270" x14ac:dyDescent="0.2">
       <c r="A8" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>101</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>102</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>8</v>
@@ -10812,32 +10812,32 @@
         <v>400</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="225" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="14" t="s">
         <v>105</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>106</v>
       </c>
       <c r="D9" s="15">
         <v>404</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="350" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>8</v>
@@ -10846,21 +10846,21 @@
         <v>400</v>
       </c>
       <c r="E10" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="G10" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="365" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>8</v>
@@ -10869,18 +10869,18 @@
         <v>400</v>
       </c>
       <c r="E11" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="253" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>8</v>
@@ -10889,15 +10889,15 @@
         <v>400</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="225" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>8</v>
@@ -10906,15 +10906,15 @@
         <v>400</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="267" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>8</v>
@@ -10923,15 +10923,15 @@
         <v>400</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="281" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>8</v>
@@ -10940,15 +10940,15 @@
         <v>400</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="253" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>8</v>
@@ -10957,12 +10957,12 @@
         <v>400</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>8</v>
@@ -10973,10 +10973,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D18" s="15">
         <v>404</v>
@@ -10984,7 +10984,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>8</v>
@@ -10995,10 +10995,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>134</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>135</v>
       </c>
       <c r="D20" s="15">
         <v>200</v>
@@ -11006,24 +11006,24 @@
     </row>
     <row r="21" spans="1:5" ht="60" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>136</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>137</v>
       </c>
       <c r="D21" s="15">
         <v>404</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D22" s="15">
         <v>401</v>
@@ -11031,10 +11031,10 @@
     </row>
     <row r="23" spans="1:5" ht="45" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>140</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>141</v>
       </c>
       <c r="D23" s="15">
         <v>404</v>
@@ -11095,19 +11095,19 @@
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="E2" s="1">
         <v>201</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -11181,13 +11181,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="E1" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>9</v>
@@ -11195,13 +11195,13 @@
     </row>
     <row r="2" spans="1:6" ht="333" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2" s="4">
         <v>201</v>
@@ -11209,13 +11209,13 @@
     </row>
     <row r="3" spans="1:6" ht="380" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="8">
         <v>201</v>
@@ -11223,13 +11223,13 @@
     </row>
     <row r="4" spans="1:6" ht="380" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" s="8">
         <v>201</v>
@@ -11237,13 +11237,13 @@
     </row>
     <row r="5" spans="1:6" ht="304" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="8">
         <v>201</v>
@@ -11251,13 +11251,13 @@
     </row>
     <row r="6" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>26</v>
-      </c>
       <c r="C6" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" s="8">
         <v>400</v>
@@ -11265,13 +11265,13 @@
     </row>
     <row r="7" spans="1:6" ht="380" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="C7" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="8">
         <v>400</v>
@@ -11279,13 +11279,13 @@
     </row>
     <row r="8" spans="1:6" ht="380" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" s="8">
         <v>400</v>
@@ -11293,13 +11293,13 @@
     </row>
     <row r="9" spans="1:6" ht="380" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="8">
         <v>400</v>
@@ -11307,13 +11307,13 @@
     </row>
     <row r="10" spans="1:6" ht="304" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="8">
         <v>400</v>
@@ -11321,13 +11321,13 @@
     </row>
     <row r="11" spans="1:6" ht="304" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>36</v>
-      </c>
       <c r="C11" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" s="8">
         <v>400</v>
@@ -11335,13 +11335,13 @@
     </row>
     <row r="12" spans="1:6" ht="304" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="C12" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D12" s="8">
         <v>400</v>
@@ -11349,13 +11349,13 @@
     </row>
     <row r="13" spans="1:6" ht="304" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="C13" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="8">
         <v>400</v>
@@ -11363,13 +11363,13 @@
     </row>
     <row r="14" spans="1:6" ht="304" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14" s="8">
         <v>400</v>
@@ -11377,13 +11377,13 @@
     </row>
     <row r="15" spans="1:6" ht="304" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="C15" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" s="8">
         <v>400</v>
@@ -11391,13 +11391,13 @@
     </row>
     <row r="16" spans="1:6" ht="304" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="C16" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D16" s="8">
         <v>400</v>
@@ -11405,70 +11405,70 @@
     </row>
     <row r="17" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>47</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>48</v>
       </c>
       <c r="D17" s="8">
         <v>200</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="8">
         <v>404</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D19" s="8">
         <v>405</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20" s="8">
         <v>401</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B21"/>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D21">
         <v>404</v>
@@ -11476,11 +11476,11 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D22" s="19">
         <v>405</v>
@@ -11489,11 +11489,11 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B23"/>
       <c r="C23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D23">
         <v>401</v>
@@ -11501,78 +11501,78 @@
     </row>
     <row r="24" spans="1:6" ht="96" x14ac:dyDescent="0.2">
       <c r="A24" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="C24" s="19" t="s">
         <v>148</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>149</v>
       </c>
       <c r="D24" s="19">
         <v>200</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="96" x14ac:dyDescent="0.2">
       <c r="A25" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B25" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="B25" s="20" t="s">
-        <v>152</v>
-      </c>
       <c r="C25" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D25" s="19">
         <v>200</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="96" x14ac:dyDescent="0.2">
       <c r="A26" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>154</v>
-      </c>
       <c r="C26" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D26" s="19">
         <v>200</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A27" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>156</v>
-      </c>
       <c r="C27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D27" s="8">
         <v>404</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A28" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>157</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>158</v>
       </c>
       <c r="D28" s="8">
         <v>404</v>
@@ -11580,56 +11580,56 @@
     </row>
     <row r="29" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" s="20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D29" s="8">
         <v>405</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D30" s="8">
         <v>401</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="112" x14ac:dyDescent="0.2">
       <c r="A31" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="B31" s="20" t="s">
-        <v>162</v>
-      </c>
       <c r="C31" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D31" s="19">
         <v>200</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B32" s="19"/>
       <c r="C32" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D32" s="19">
         <v>200</v>

--- a/src/test/resources/Team01_RestAssured_Rebels_TestDataSheet.xlsx
+++ b/src/test/resources/Team01_RestAssured_Rebels_TestDataSheet.xlsx
@@ -5,13 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Batch" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Program" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="User" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="ForgotPassword" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Batch" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Program" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="User" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="82">
   <si>
     <t xml:space="preserve">ScenarioName</t>
   </si>
@@ -43,6 +44,11 @@
     <t xml:space="preserve">Valid credential</t>
   </si>
   <si>
+    <t xml:space="preserve">{
+"userLoginEmailId":"VALID_EMAIL", "password":"VALID_PASS"
+}</t>
+  </si>
+  <si>
     <t xml:space="preserve">Invalid method</t>
   </si>
   <si>
@@ -59,8 +65,8 @@
   </si>
   <si>
     <t xml:space="preserve">{
-"userLoginEmailId":"",
-"password":"adm123"
+"userLoginEmailId":"", 
+"password":"VALID_PASS"
 }</t>
   </si>
   <si>
@@ -68,8 +74,8 @@
   </si>
   <si>
     <t xml:space="preserve">{
-"userLoginEmailId":"@#$",
-"password":"x"
+"userLoginEmailId":"@#$VALID_EMAIL", 
+"password":"VALID_PASS"
 }</t>
   </si>
   <si>
@@ -77,18 +83,15 @@
   </si>
   <si>
     <t xml:space="preserve">{
-"userLoginEmailId":"test @gmail.com",
-"password":"12345"
-}
-</t>
+"userLoginEmailId":" VALID_EMAIL", "password":"VALID_PASS"}</t>
   </si>
   <si>
     <t xml:space="preserve">Null in email field</t>
   </si>
   <si>
     <t xml:space="preserve">{
-"userLoginEmailId":null,
-"password":"aqwerp123"
+"userLoginEmailId":null, 
+"password":"VALID_PASS"
 }</t>
   </si>
   <si>
@@ -96,8 +99,7 @@
   </si>
   <si>
     <t xml:space="preserve">{
-"userLoginEmailId":"pasha.12@gmail.com",
-"password":"adm123"
+"userLoginEmailId":"pasha.12@gmail.com", "password":"VALID_PASS"
 }</t>
   </si>
   <si>
@@ -105,7 +107,7 @@
   </si>
   <si>
     <t xml:space="preserve">{
-"userLoginEmailId":"Team01@gmail.com",
+"userLoginEmailId":"VALID_EMAIL", 
 "password":" "
 }</t>
   </si>
@@ -114,8 +116,7 @@
   </si>
   <si>
     <t xml:space="preserve">{
-"userLoginEmailId":"Team01@gmail.com",
-"password":"Abc@1234$"
+"userLoginEmailId":"VALID_EMAIL", "password":"#@VALID_PASS"
 }</t>
   </si>
   <si>
@@ -123,8 +124,8 @@
   </si>
   <si>
     <t xml:space="preserve">{
-"userLoginEmailId":"Team01@gmail.com",
-"password":"adm 123"
+"userLoginEmailId":"VALID_EMAIL",
+ "password":"VALID_PASS  "
 }</t>
   </si>
   <si>
@@ -132,7 +133,7 @@
   </si>
   <si>
     <t xml:space="preserve">{
-"userLoginEmailId":"Team01@gmail.com",
+"userLoginEmailId":"VALID_EMAIL", 
 "password":null
 }</t>
   </si>
@@ -141,12 +142,54 @@
   </si>
   <si>
     <t xml:space="preserve">{
-"userLoginEmailId":"inactive@gmail.com",
-"password":"inactive123"
+"userLoginEmailId":"inactive@gmail.com", "password":"inactive123"
 }</t>
   </si>
   <si>
     <t xml:space="preserve">Without request body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valid email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+"userLoginEmailId":"VALID_EMAIL"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">But Given gherkin has 200 status code. 
+201 status API sends email for reset password 
+Request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+"userLoginEmailId":"VALID_EMAIL"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+"userLoginEmailId":""
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invalid email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+"userLoginEmailId":"Ev@@gmail.com"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Null email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+{"userLoginEmailId":null}
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+"userLoginEmailId":"admin.12@gmail.com"
+}</t>
   </si>
   <si>
     <t xml:space="preserve">CreateBatch_Valid_batchName</t>
@@ -403,7 +446,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,6 +477,19 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -456,14 +512,13 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -530,7 +585,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -542,24 +597,44 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -570,7 +645,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -578,31 +653,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -807,7 +862,7 @@
   <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44.46"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
@@ -833,11 +888,13 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" customFormat="false" ht="13.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="51.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="n">
         <v>200</v>
@@ -848,7 +905,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -861,7 +918,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -874,7 +931,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="2"/>
@@ -887,7 +944,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -900,10 +957,10 @@
     </row>
     <row r="7" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3" t="s">
         <v>11</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="n">
@@ -913,12 +970,12 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="42.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="4" t="s">
         <v>13</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>14</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="n">
@@ -928,12 +985,12 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="55.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="33.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="3" t="s">
         <v>15</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="n">
@@ -944,11 +1001,11 @@
       <c r="G9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="8" t="s">
         <v>17</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="n">
@@ -959,11 +1016,11 @@
       <c r="G10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>19</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="n">
@@ -974,11 +1031,11 @@
       <c r="G11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>21</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="n">
@@ -990,10 +1047,10 @@
     </row>
     <row r="13" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="9" t="s">
         <v>23</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="n">
@@ -1005,10 +1062,10 @@
     </row>
     <row r="14" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="3" t="s">
         <v>25</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="n">
@@ -1020,10 +1077,10 @@
     </row>
     <row r="15" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="9" t="s">
         <v>27</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="n">
@@ -1035,10 +1092,10 @@
     </row>
     <row r="16" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="9" t="s">
         <v>29</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>30</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="n">
@@ -1050,7 +1107,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -1153,7 +1210,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
+      <c r="B28" s="9"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -1171,7 +1228,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
+      <c r="B30" s="9"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -1199,7 +1256,7 @@
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="10"/>
+      <c r="C33" s="12"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -9945,14 +10002,6 @@
       <c r="G1004" s="2"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B11" r:id="rId1" display="pasha.12@gmail.com"/>
-    <hyperlink ref="B12" r:id="rId2" display="Team01@gmail.com"/>
-    <hyperlink ref="B13" r:id="rId3" display="Team01@gmail.com"/>
-    <hyperlink ref="B14" r:id="rId4" display="Team01@gmail.com"/>
-    <hyperlink ref="B15" r:id="rId5" display="Team01@gmail.com"/>
-    <hyperlink ref="B16" r:id="rId6" display="inactive@gmail.com"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -9968,161 +10017,128 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="36.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="33.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="11" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="19.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="11" width="14.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="33.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="35.35"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="11" t="s">
+      <c r="C1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="D1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-    </row>
-    <row r="2" customFormat="false" ht="73.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="13" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="33.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="B2" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="11" t="n">
+      <c r="C2" s="0" t="n">
         <v>201</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-    </row>
-    <row r="3" customFormat="false" ht="73.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
+      <c r="E2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="13" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="21.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="0" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="32.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="16" t="n">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="73.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
+      <c r="C5" s="0" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="33.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C6" s="0" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="32.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="16" t="n">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="83.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
+      <c r="B7" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="C7" s="0" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="32.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="73.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
+      <c r="B8" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="C8" s="0" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="33.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="16" t="n">
+      <c r="C9" s="0" t="n">
         <v>400</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="73.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="21" t="n">
-        <v>401</v>
-      </c>
-      <c r="E7" s="0"/>
-    </row>
-    <row r="8" customFormat="false" ht="73.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>400</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>46</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B9" r:id="rId1" display="admin.12@gmail.com"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -10132,121 +10148,152 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="8.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="11" width="12.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="16" width="36.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="33.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="19.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="14.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+    </row>
+    <row r="2" customFormat="false" ht="73.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="16" t="n">
+        <v>201</v>
+      </c>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" ht="73.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="21" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="73.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-    </row>
-    <row r="2" customFormat="false" ht="142.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+      <c r="B4" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="C4" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="21" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="83.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="B5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="C5" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="73.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="12" t="n">
-        <v>201</v>
-      </c>
-      <c r="F2" s="12" t="s">
+      <c r="B6" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
-      <c r="V3" s="12"/>
-      <c r="W3" s="12"/>
-      <c r="X3" s="12"/>
-      <c r="Y3" s="12"/>
-      <c r="Z3" s="12"/>
+      <c r="C6" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="73.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="73.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="21" t="n">
+        <v>400</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -10260,6 +10307,138 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:Z3"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="8.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="27.03"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+      <c r="X1" s="17"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="17"/>
+    </row>
+    <row r="2" customFormat="false" ht="142.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>201</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17"/>
+      <c r="Z2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="17"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -10282,21 +10461,21 @@
         <v>1</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="261.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D2" s="22" t="n">
         <v>201</v>
@@ -10304,13 +10483,13 @@
     </row>
     <row r="3" customFormat="false" ht="272.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="22" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D3" s="23" t="n">
         <v>201</v>
@@ -10318,13 +10497,13 @@
     </row>
     <row r="4" customFormat="false" ht="261.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="22" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D4" s="23" t="n">
         <v>201</v>
@@ -10332,71 +10511,71 @@
     </row>
     <row r="5" customFormat="false" ht="207.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="22" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D5" s="23" t="n">
         <v>201</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="7" t="n">
+      <c r="A6" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>200</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="7" t="n">
+      <c r="A7" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>404</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="7" t="n">
+      <c r="A8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>405</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="44.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="7" t="n">
+      <c r="A9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>401</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/src/test/resources/Team01_RestAssured_Rebels_TestDataSheet.xlsx
+++ b/src/test/resources/Team01_RestAssured_Rebels_TestDataSheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dineshdeshmukh/eclipse-workspace/Team01_RestAssured_Rebels/src/test/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dineshdeshmukh/latestprogram/Team01_RestAssured_Rebels/src/test/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE98D28-7889-C541-8264-742F804F3225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C8B10F-95BE-0B42-BFAF-54ECF5EBFA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="19420" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="190">
   <si>
     <t>ScenarioName</t>
   </si>
@@ -1285,12 +1285,48 @@
   <si>
     <t>Get_Active_Inactive_User_Count_Without_Authorization</t>
   </si>
+  <si>
+    <t>GetAll_BatchById_Valid_BatchId</t>
+  </si>
+  <si>
+    <t>/batches/batchId/{batchId}</t>
+  </si>
+  <si>
+    <t>GetBatchById_InvalidBatchId</t>
+  </si>
+  <si>
+    <t>/batches/batchId/9999</t>
+  </si>
+  <si>
+    <t>Batch not found with Id</t>
+  </si>
+  <si>
+    <t>GetBatch_ById_NoAuth</t>
+  </si>
+  <si>
+    <t>GetBatchById_Invalid_Endpoint</t>
+  </si>
+  <si>
+    <t>/batches/batid/9999</t>
+  </si>
+  <si>
+    <t>GetAll_Valid_Batches</t>
+  </si>
+  <si>
+    <t>GetAll_Batches_InvalidEndpoint</t>
+  </si>
+  <si>
+    <t>/batch</t>
+  </si>
+  <si>
+    <t>GetAll_Batches_With_NoAuth</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1365,6 +1401,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1D1C1D"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1392,7 +1444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1455,6 +1507,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10926,7 +10980,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.33203125" customWidth="1"/>
@@ -11071,6 +11125,89 @@
       </c>
       <c r="E8" s="16" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="25"/>
+      <c r="C9" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="24">
+        <v>200</v>
+      </c>
+      <c r="E9" s="25"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D10">
+        <v>404</v>
+      </c>
+      <c r="E10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D12">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="25"/>
+      <c r="C13" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="24">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D14">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15">
+        <v>401</v>
       </c>
     </row>
   </sheetData>
